--- a/templates/秋招个人资料库模板.xlsx
+++ b/templates/秋招个人资料库模板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Raef3f8bbd8cb46f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人资料" sheetId="2" r:id="R93b68f64c65b4361"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历清单" sheetId="3" r:id="Rb21e9411df0043ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件清单" sheetId="4" r:id="R81ff27d21aae4c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R08a51f348e51488b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人资料" sheetId="2" r:id="Rb28c2a59460242e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历清单" sheetId="3" r:id="R51a90591dfb745c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件清单" sheetId="4" r:id="Re31e8d1ff39441d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -621,7 +621,7 @@
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>

--- a/templates/秋招个人资料库模板.xlsx
+++ b/templates/秋招个人资料库模板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R08a51f348e51488b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人资料" sheetId="2" r:id="Rb28c2a59460242e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历清单" sheetId="3" r:id="R51a90591dfb745c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件清单" sheetId="4" r:id="Re31e8d1ff39441d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Reb051ff2fcec465d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人资料" sheetId="2" r:id="Rbae720b505fd4159"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历清单" sheetId="3" r:id="R903a21ffccad498d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件清单" sheetId="4" r:id="R6420a79015fb4cce"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/templates/秋招个人资料库模板.xlsx
+++ b/templates/秋招个人资料库模板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Reb051ff2fcec465d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人资料" sheetId="2" r:id="Rbae720b505fd4159"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历清单" sheetId="3" r:id="R903a21ffccad498d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件清单" sheetId="4" r:id="R6420a79015fb4cce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Rc4abe87696f44433"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人资料" sheetId="2" r:id="R67775a9922194acf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历清单" sheetId="3" r:id="R7b0324070abd4b45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件清单" sheetId="4" r:id="R1c113d2884a14784"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/templates/秋招个人资料库模板.xlsx
+++ b/templates/秋招个人资料库模板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Rc4abe87696f44433"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人资料" sheetId="2" r:id="R67775a9922194acf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历清单" sheetId="3" r:id="R7b0324070abd4b45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件清单" sheetId="4" r:id="R1c113d2884a14784"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R8673419954d74588"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人资料" sheetId="2" r:id="Rb1aa88547f6b459e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历清单" sheetId="3" r:id="Rdb0a0f7e6f4e49f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件清单" sheetId="4" r:id="Rbcbcd0fe5b8a4fb1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/templates/秋招个人资料库模板.xlsx
+++ b/templates/秋招个人资料库模板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R077cf2ffdbde4dc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人资料" sheetId="2" r:id="R9ce469342f334261"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历清单" sheetId="3" r:id="R2e9f1b1616e8496f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件清单" sheetId="4" r:id="R48a7146b768b4c0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Rc352cb8fa4da4118"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人资料" sheetId="2" r:id="R35ee9984f0984a56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历清单" sheetId="3" r:id="Rf306c1563e3e41b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件清单" sheetId="4" r:id="Rd1e9800156d24092"/>
   </x:sheets>
 </x:workbook>
 </file>
